--- a/emprical_info.xlsx
+++ b/emprical_info.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="88">
   <si>
     <t>name</t>
   </si>
@@ -137,9 +137,6 @@
   </si>
   <si>
     <t>12.3k</t>
-  </si>
-  <si>
-    <t>303.6k</t>
   </si>
   <si>
     <t>sing-box-for-android</t>
@@ -1992,8 +1989,8 @@
       <c r="B68" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C68" t="s">
-        <v>36</v>
+      <c r="C68">
+        <v>303600</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -2009,7 +2006,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B70" s="1">
         <v>717</v>
@@ -2031,10 +2028,10 @@
     </row>
     <row r="72" ht="15.75" spans="1:3">
       <c r="A72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C72">
         <v>88762</v>
@@ -2086,10 +2083,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C77">
         <v>371029</v>
@@ -2097,7 +2094,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>16</v>
@@ -2108,10 +2105,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
+        <v>42</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C79">
         <v>900774</v>
@@ -2119,10 +2116,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
+        <v>39</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C80">
         <v>371029</v>
@@ -2130,10 +2127,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C81">
         <v>79258</v>
@@ -2152,7 +2149,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B83" s="1">
         <v>270</v>
@@ -2185,7 +2182,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B86" s="1">
         <v>632</v>
@@ -2196,7 +2193,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>16</v>
@@ -2207,7 +2204,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B88" s="1">
         <v>368</v>
@@ -2218,10 +2215,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
+        <v>49</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C89">
         <v>33430</v>
@@ -2229,10 +2226,10 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
+        <v>42</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C90">
         <v>900774</v>
@@ -2240,7 +2237,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B91" s="1">
         <v>363</v>
@@ -2251,10 +2248,10 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
+        <v>42</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C92">
         <v>900774</v>
@@ -2267,8 +2264,8 @@
       <c r="B93" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C93" t="s">
-        <v>36</v>
+      <c r="C93">
+        <v>303600</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -2278,13 +2275,13 @@
       <c r="B94" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C94" t="s">
-        <v>36</v>
+      <c r="C94">
+        <v>303600</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B95" s="1">
         <v>351</v>
@@ -2300,16 +2297,16 @@
       <c r="B96" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C96" t="s">
-        <v>36</v>
+      <c r="C96">
+        <v>303600</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" t="s">
+        <v>53</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="C97">
         <v>143120</v>
@@ -2317,7 +2314,7 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B98" s="1">
         <v>351</v>
@@ -2328,7 +2325,7 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B99" s="1">
         <v>988</v>
@@ -2339,7 +2336,7 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B100" s="1">
         <v>212</v>
@@ -2350,10 +2347,10 @@
     </row>
     <row r="101" ht="15.75" spans="1:3">
       <c r="A101" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C101">
         <v>88762</v>
@@ -2372,7 +2369,7 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B103" s="1">
         <v>628</v>
@@ -2399,8 +2396,8 @@
       <c r="B105" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C105" t="s">
-        <v>36</v>
+      <c r="C105">
+        <v>303600</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -2416,10 +2413,10 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" t="s">
+        <v>58</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C107">
         <v>212043</v>
@@ -2438,7 +2435,7 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B109" s="1">
         <v>181</v>
@@ -2449,10 +2446,10 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110" t="s">
+        <v>61</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C110">
         <v>110253</v>
@@ -2471,7 +2468,7 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B112" s="1">
         <v>208</v>
@@ -2493,10 +2490,10 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114" t="s">
+        <v>61</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C114">
         <v>110253</v>
@@ -2509,13 +2506,13 @@
       <c r="B115" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C115" t="s">
-        <v>36</v>
+      <c r="C115">
+        <v>303600</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B116" s="1">
         <v>110</v>
@@ -2526,10 +2523,10 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
+        <v>61</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C117">
         <v>110253</v>
@@ -2548,7 +2545,7 @@
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B119" s="1">
         <v>836</v>
@@ -2592,7 +2589,7 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B123" s="1">
         <v>351</v>
@@ -2603,7 +2600,7 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B124" s="1">
         <v>351</v>
@@ -2614,10 +2611,10 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
+        <v>66</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C125">
         <v>446442</v>
@@ -2636,7 +2633,7 @@
     </row>
     <row r="127" spans="1:3">
       <c r="A127" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B127" s="1">
         <v>274</v>
@@ -2647,10 +2644,10 @@
     </row>
     <row r="128" spans="1:3">
       <c r="A128" t="s">
+        <v>61</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C128">
         <v>110253</v>
@@ -2669,7 +2666,7 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B130" s="1">
         <v>836</v>
@@ -2680,10 +2677,10 @@
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
+        <v>66</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C131">
         <v>446442</v>
@@ -2691,10 +2688,10 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
+        <v>66</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C132">
         <v>446442</v>
@@ -2702,7 +2699,7 @@
     </row>
     <row r="133" spans="1:3">
       <c r="A133" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B133" s="1">
         <v>836</v>
@@ -2713,7 +2710,7 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B134" s="1">
         <v>836</v>
@@ -2724,7 +2721,7 @@
     </row>
     <row r="135" spans="1:3">
       <c r="A135" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B135" s="1">
         <v>836</v>
@@ -2735,7 +2732,7 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B136" s="1">
         <v>836</v>
@@ -2746,7 +2743,7 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>18</v>
@@ -2757,7 +2754,7 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B138" s="1">
         <v>836</v>
@@ -2768,7 +2765,7 @@
     </row>
     <row r="139" spans="1:3">
       <c r="A139" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B139" s="1">
         <v>836</v>
@@ -2779,7 +2776,7 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B140" s="1">
         <v>836</v>
@@ -2790,7 +2787,7 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B141" s="1">
         <v>160</v>
@@ -2801,7 +2798,7 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B142" s="1">
         <v>836</v>
@@ -2812,7 +2809,7 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B143" s="1">
         <v>593</v>
@@ -2823,7 +2820,7 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B144" s="1">
         <v>405</v>
@@ -2834,7 +2831,7 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B145" s="1">
         <v>836</v>
@@ -2845,7 +2842,7 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>10</v>
@@ -2856,7 +2853,7 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>10</v>
@@ -2867,10 +2864,10 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148" t="s">
+        <v>44</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C148">
         <v>79258</v>
@@ -2878,7 +2875,7 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B149" s="1">
         <v>516</v>
@@ -2889,7 +2886,7 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B150" s="1">
         <v>516</v>
@@ -2900,10 +2897,10 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151" t="s">
+        <v>44</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C151">
         <v>79258</v>
@@ -2922,10 +2919,10 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C153">
         <v>371029</v>
@@ -2933,7 +2930,7 @@
     </row>
     <row r="154" spans="1:3">
       <c r="A154" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B154" s="1">
         <v>110</v>
@@ -2944,7 +2941,7 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B155" s="1">
         <v>851</v>
@@ -2971,8 +2968,8 @@
       <c r="B157" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C157" t="s">
-        <v>36</v>
+      <c r="C157">
+        <v>303600</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -2982,16 +2979,16 @@
       <c r="B158" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C158" t="s">
-        <v>36</v>
+      <c r="C158">
+        <v>303600</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" t="s">
+        <v>78</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C159">
         <v>1026294</v>
@@ -2999,10 +2996,10 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160" t="s">
+        <v>78</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C160">
         <v>1026294</v>
@@ -3010,10 +3007,10 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161" t="s">
+        <v>44</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C161">
         <v>79258</v>
@@ -3021,10 +3018,10 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C162">
         <v>1890734</v>
@@ -3065,10 +3062,10 @@
     </row>
     <row r="166" spans="1:3">
       <c r="A166" t="s">
+        <v>81</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C166">
         <v>90748</v>
@@ -3076,7 +3073,7 @@
     </row>
     <row r="167" spans="1:3">
       <c r="A167" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>23</v>
@@ -3092,8 +3089,8 @@
       <c r="B168" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C168" t="s">
-        <v>36</v>
+      <c r="C168">
+        <v>303600</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -3103,16 +3100,16 @@
       <c r="B169" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C169" t="s">
-        <v>36</v>
+      <c r="C169">
+        <v>303600</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170" t="s">
+        <v>44</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C170">
         <v>79258</v>
@@ -3120,10 +3117,10 @@
     </row>
     <row r="171" spans="1:3">
       <c r="A171" t="s">
+        <v>44</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C171">
         <v>79258</v>
@@ -3131,10 +3128,10 @@
     </row>
     <row r="172" spans="1:3">
       <c r="A172" t="s">
+        <v>44</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C172">
         <v>79258</v>
@@ -3142,10 +3139,10 @@
     </row>
     <row r="173" spans="1:3">
       <c r="A173" t="s">
+        <v>44</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C173">
         <v>79258</v>
@@ -3153,10 +3150,10 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174" t="s">
+        <v>44</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C174">
         <v>79258</v>
@@ -3164,10 +3161,10 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175" t="s">
+        <v>44</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C175">
         <v>79258</v>
@@ -3175,10 +3172,10 @@
     </row>
     <row r="176" spans="1:3">
       <c r="A176" t="s">
+        <v>44</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C176">
         <v>79258</v>
@@ -3186,10 +3183,10 @@
     </row>
     <row r="177" spans="1:3">
       <c r="A177" t="s">
+        <v>44</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C177">
         <v>79258</v>
@@ -3197,10 +3194,10 @@
     </row>
     <row r="178" spans="1:3">
       <c r="A178" t="s">
+        <v>44</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C178">
         <v>79258</v>
@@ -3208,10 +3205,10 @@
     </row>
     <row r="179" spans="1:3">
       <c r="A179" t="s">
+        <v>44</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C179">
         <v>79258</v>
@@ -3219,10 +3216,10 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180" t="s">
+        <v>44</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C180">
         <v>79258</v>
@@ -3230,10 +3227,10 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181" t="s">
+        <v>44</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C181">
         <v>79258</v>
@@ -3241,10 +3238,10 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182" t="s">
+        <v>44</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C182">
         <v>79258</v>
@@ -3252,10 +3249,10 @@
     </row>
     <row r="183" spans="1:3">
       <c r="A183" t="s">
+        <v>44</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C183">
         <v>79258</v>
@@ -3263,10 +3260,10 @@
     </row>
     <row r="184" spans="1:3">
       <c r="A184" t="s">
+        <v>84</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="C184">
         <v>1074744</v>
@@ -3274,7 +3271,7 @@
     </row>
     <row r="185" spans="1:3">
       <c r="A185" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B185" s="1">
         <v>181</v>
@@ -3285,10 +3282,10 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186" t="s">
+        <v>78</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C186">
         <v>1026294</v>
@@ -3296,10 +3293,10 @@
     </row>
     <row r="187" spans="1:3">
       <c r="A187" t="s">
+        <v>78</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C187">
         <v>1026294</v>
@@ -3307,10 +3304,10 @@
     </row>
     <row r="188" spans="1:3">
       <c r="A188" t="s">
+        <v>78</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C188">
         <v>1026294</v>
@@ -3318,10 +3315,10 @@
     </row>
     <row r="189" spans="1:3">
       <c r="A189" t="s">
+        <v>78</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C189">
         <v>1026294</v>
@@ -3329,10 +3326,10 @@
     </row>
     <row r="190" spans="1:3">
       <c r="A190" t="s">
+        <v>78</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C190">
         <v>1026294</v>
@@ -3340,10 +3337,10 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191" t="s">
+        <v>78</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C191">
         <v>1026294</v>
@@ -3351,10 +3348,10 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
+        <v>78</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C192">
         <v>1026294</v>
@@ -3362,10 +3359,10 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193" t="s">
+        <v>78</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C193">
         <v>1026294</v>
@@ -3373,10 +3370,10 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194" t="s">
+        <v>78</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B194" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C194">
         <v>1026294</v>
@@ -3384,10 +3381,10 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195" t="s">
+        <v>78</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C195">
         <v>1026294</v>
@@ -3395,10 +3392,10 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196" t="s">
+        <v>78</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C196">
         <v>1026294</v>
@@ -3406,10 +3403,10 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197" t="s">
+        <v>78</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C197">
         <v>1026294</v>
@@ -3417,10 +3414,10 @@
     </row>
     <row r="198" spans="1:3">
       <c r="A198" t="s">
+        <v>78</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C198">
         <v>1026294</v>
@@ -3428,10 +3425,10 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199" t="s">
+        <v>78</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="C199">
         <v>1026294</v>
@@ -3461,7 +3458,7 @@
     </row>
     <row r="202" spans="1:3">
       <c r="A202" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B202" s="1">
         <v>2500</v>
@@ -3472,10 +3469,10 @@
     </row>
     <row r="203" spans="1:3">
       <c r="A203" t="s">
+        <v>44</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="C203">
         <v>79258</v>
